--- a/artfynd/A 21475-2026 artfynd.xlsx
+++ b/artfynd/A 21475-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120663051</v>
       </c>
       <c r="B2" t="n">
-        <v>90675</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,53 +772,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120662814</v>
+        <v>120749701</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>3518</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Haradsområdet, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761155</v>
+        <v>761180</v>
       </c>
       <c r="R3" t="n">
-        <v>7335711</v>
+        <v>7335735</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,56 +873,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120749701</v>
+        <v>120662814</v>
       </c>
       <c r="B4" t="n">
-        <v>84287</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3518</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Haradsområdet, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761180</v>
+        <v>761155</v>
       </c>
       <c r="R4" t="n">
-        <v>7335735</v>
+        <v>7335711</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,6 +967,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120663046</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Haradsområdet, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>761568</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7335558</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sofia Hagsand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21475-2026 artfynd.xlsx
+++ b/artfynd/A 21475-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663051</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120749701</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120662814</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,8 +1084,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120663046</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>